--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A766C38A-78CC-4713-9649-9003B609E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B37E6A5-1B0A-4E44-AD6E-045624435D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="5063" windowWidth="23790" windowHeight="7372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
-  <si>
-    <t>Item_Equip_Hat_1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>Icon/Icon_Item_Corn</t>
   </si>
@@ -70,9 +67,6 @@
     <t>SellingPrice</t>
   </si>
   <si>
-    <t>Item_DummyBox_1</t>
-  </si>
-  <si>
     <t>MaxStackCount</t>
   </si>
   <si>
@@ -83,12 +77,6 @@
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
   </si>
   <si>
     <t>Description</t>
@@ -143,13 +131,126 @@
   </si>
   <si>
     <t>Icon/Icon_Item_Carrot</t>
+  </si>
+  <si>
+    <t>UseItemType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomItemBox</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatChangeHp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatChangeAtk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SummonMonster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RandomItemBox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의 파라미터는 획득할 수 있는 아이템 Id 리스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>StatChangeAtk의 파라미터는 음수 양수로 ATK 버프 디버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+StatChangeHP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의 파라미터는 음수 양수로 HP 버프 디버프
+SummonMonster의 파라미터는 소환할 수 있는 몬스터의 Id 리스트</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_DummyBox_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Equip_Hat_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Corn_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Gold_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Equip_Hat_1,Item_Corn_1,Item_Gold_1:100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_bear_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseItemParameterList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -173,6 +274,26 @@
       <sz val="8"/>
       <name val="돋움"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -255,7 +376,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -279,6 +400,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,7 +595,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -472,7 +604,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -694,94 +826,111 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.3984375" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.59765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="50.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="2" customWidth="1"/>
     <col min="5" max="7" width="12.59765625" style="2"/>
     <col min="8" max="8" width="28.3984375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.59765625" style="2"/>
+    <col min="9" max="9" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.1328125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="12.59765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" s="16" customFormat="1" ht="137.25" customHeight="1">
+      <c r="A1" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.15">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="13.15">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>20</v>
@@ -790,24 +939,30 @@
         <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
         <v>1000</v>
@@ -816,24 +971,24 @@
         <v>1000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -842,24 +997,30 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
         <v>100</v>
@@ -868,24 +1029,30 @@
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>20</v>
@@ -894,24 +1061,30 @@
         <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -920,40 +1093,46 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+        <v>35</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAD6CBD-0401-4EF0-A6D4-BB0DB0989F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9445D22B-1446-4073-8111-511DE8D710D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6578" yWindow="2325" windowWidth="17984" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6915" yWindow="2663" windowWidth="17985" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
-  <si>
-    <t>Icon/Icon_Item_Corn</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>상자다. 딱히 의미가 있진 않다.</t>
   </si>
@@ -31,9 +28,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>옥수수다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -113,9 +107,6 @@
   </si>
   <si>
     <t>감자</t>
-  </si>
-  <si>
-    <t>감자다. 딱히 의미가 있진 않다.</t>
   </si>
   <si>
     <t>Item_Carrot_1</t>
@@ -124,13 +115,6 @@
   <si>
     <t>당근</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근. 먹으면 기분이 좋아진다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Carrot</t>
   </si>
   <si>
     <t>UseItemType</t>
@@ -238,11 +222,38 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>70,20,1</t>
+    <t>Carrot</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Carrot</t>
+    <t>먹으면 힘이 솟아나는 옥수수. 
+공격력 + 20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있는 감자.
+HP + 30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>70,30,1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄청난 힘을 제공하는 신비한 당근.
+HP + 70 / 공격력 + 30/ 스킬카드 획득 중 1개를 선택할 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Carrot[Carrot_1]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Items[Icon_Corn]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Items[Icon_Potato]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -849,95 +860,95 @@
   <sheetData>
     <row r="1" spans="1:10" ht="137.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.15">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="5" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="3">
         <v>20</v>
@@ -946,30 +957,30 @@
         <v>100</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3">
         <v>1000</v>
@@ -978,24 +989,24 @@
         <v>1000</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -1004,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J6" s="3">
         <v>700</v>
@@ -1015,19 +1026,19 @@
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
@@ -1035,11 +1046,11 @@
       <c r="G7" s="3">
         <v>20</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>0</v>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J7" s="3">
         <v>20</v>
@@ -1047,19 +1058,19 @@
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3">
         <v>20</v>
@@ -1067,31 +1078,31 @@
       <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>27</v>
+      <c r="H8" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J8" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="25.5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="51.4">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3">
         <v>20</v>
@@ -1099,14 +1110,14 @@
       <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
+      <c r="H9" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9445D22B-1446-4073-8111-511DE8D710D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C65EFC8-1A86-475C-B32F-D348E9CB92FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="2663" windowWidth="17985" windowHeight="10192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>상자다. 딱히 의미가 있진 않다.</t>
   </si>
@@ -254,6 +254,14 @@
   </si>
   <si>
     <t>Icon/Icon_Items[Icon_Potato]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChangeHp,ChangeAtk,GetSkillCard</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseItemSelectableBuffList</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -842,7 +850,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.3984375" style="3" customWidth="1"/>
@@ -855,10 +863,12 @@
     <col min="8" max="8" width="26.1328125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="42.46484375" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="12.59765625" style="3"/>
+    <col min="11" max="11" width="31.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.59765625" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="12.59765625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="137.25" customHeight="1">
+    <row r="1" spans="1:11" ht="137.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -870,7 +880,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.15">
+    <row r="2" spans="1:11" ht="13.15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -901,8 +911,11 @@
       <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="15.75" customHeight="1">
+      <c r="K2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -933,8 +946,11 @@
       <c r="J3" s="6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K3" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -965,8 +981,11 @@
       <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K4" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
@@ -992,7 +1011,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -1024,7 +1043,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>39</v>
       </c>
@@ -1056,7 +1075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>24</v>
       </c>
@@ -1088,7 +1107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="51.4">
+    <row r="9" spans="1:11" ht="51.4">
       <c r="A9" s="13" t="s">
         <v>29</v>
       </c>
@@ -1120,37 +1139,37 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C65EFC8-1A86-475C-B32F-D348E9CB92FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A150538-5D25-4708-B240-0BC11C99393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
-  <si>
-    <t>상자다. 딱히 의미가 있진 않다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>string</t>
   </si>
@@ -37,24 +34,9 @@
     <t>Grade</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
-    <t>의문의 모자</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>지역에 나타나는 금화</t>
-  </si>
-  <si>
     <t>ItemType</t>
   </si>
   <si>
@@ -64,9 +46,6 @@
     <t>MaxStackCount</t>
   </si>
   <si>
-    <t>착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
@@ -79,9 +58,6 @@
     <t>IconPath</t>
   </si>
   <si>
-    <t>상자</t>
-  </si>
-  <si>
     <t>옥수수</t>
   </si>
   <si>
@@ -91,19 +67,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>화폐</t>
-  </si>
-  <si>
     <t>Item_Potato_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Box_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Equip_Hat_1</t>
   </si>
   <si>
     <t>감자</t>
@@ -118,10 +82,6 @@
   </si>
   <si>
     <t>UseItemType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomItemBox</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -194,23 +154,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Item_DummyBox_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Equip_Hat_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Item_Corn_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Gold_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Equip_Hat_1,Item_Corn_1,Item_Gold_1:100</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -240,11 +184,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>엄청난 힘을 제공하는 신비한 당근.
-HP + 70 / 공격력 + 30/ 스킬카드 획득 중 1개를 선택할 수 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon/Icon_Item_Carrot[Carrot_1]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -262,6 +201,11 @@
   </si>
   <si>
     <t>UseItemSelectableBuffList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>엄청난 힘을 제공하는 신비한 당근.
+선택) HP + 70 / 공격력 + 30 / 스킬카드 획득</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -395,7 +339,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -416,9 +360,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -870,275 +811,188 @@
   <sheetData>
     <row r="1" spans="1:11" ht="137.25" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13.15">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="13.9">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="25.9">
+      <c r="A4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="25.9">
+      <c r="A5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>10</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="51.4">
+      <c r="A6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="G6" s="3">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="3">
-        <v>20</v>
-      </c>
-      <c r="G4" s="3">
-        <v>100</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="3">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>100</v>
-      </c>
-      <c r="G7" s="3">
-        <v>20</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>20</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="J6" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="51.4">
-      <c r="A9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>20</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="9" spans="1:11" ht="12.75"/>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
@@ -1150,9 +1004,9 @@
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="7"/>
@@ -1170,104 +1024,104 @@
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
